--- a/docs/evidence/cruise-fullflow-acceptance-20261024/散位代理-manifest.xlsx
+++ b/docs/evidence/cruise-fullflow-acceptance-20261024/散位代理-manifest.xlsx
@@ -16,156 +16,171 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">姓名</t>
+          <t xml:space="preserve">Surname</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">性别</t>
+          <t xml:space="preserve">Given name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">出生日期</t>
+          <t xml:space="preserve">Gender</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">护照号</t>
+          <t xml:space="preserve">Date of birth</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">护照有效期</t>
+          <t xml:space="preserve">Nationality</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">房号</t>
+          <t xml:space="preserve">Passport number</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">签证</t>
+          <t xml:space="preserve">Expiry date</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">特殊饮食</t>
+          <t xml:space="preserve">Cabin number</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t xml:space="preserve">过敏说明</t>
+          <t xml:space="preserve">Special diet</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">资料缺口</t>
+          <t xml:space="preserve">Allergy details</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Missing documents</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ZHOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">M</t>
+          <t xml:space="preserve">MING</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990-01-01</t>
+          <t xml:space="preserve">M</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">EACCEPT0</t>
+          <t xml:space="preserve">1990-01-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-01</t>
+          <t xml:space="preserve">CHN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9234</t>
+          <t xml:space="preserve">EACCEPT0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">已齐</t>
+          <t xml:space="preserve">2032-01-01</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">无</t>
+          <t xml:space="preserve">9234</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">无</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姓名</t>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已齐</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ZHOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M</t>
+          <t xml:space="preserve">FANG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990-01-01</t>
+          <t xml:space="preserve">M</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">EACCEPT1</t>
+          <t xml:space="preserve">1990-01-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-01</t>
+          <t xml:space="preserve">CHN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9234</t>
+          <t xml:space="preserve">EACCEPT1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已齐</t>
+          <t xml:space="preserve">2032-01-01</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">无</t>
+          <t xml:space="preserve">9234</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">无</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姓名</t>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已齐</t>
         </is>
       </c>
     </row>
